--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.19546195859061</v>
+        <v>3.769262568270974</v>
       </c>
       <c r="D2" t="n">
-        <v>27.9176893759436</v>
+        <v>4.536624523590835</v>
       </c>
       <c r="E2" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F2" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.59506637504548</v>
+        <v>2.20919828594489</v>
       </c>
       <c r="D3" t="n">
-        <v>16.14964680402453</v>
+        <v>2.624317605653986</v>
       </c>
       <c r="E3" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F3" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.97156498244657</v>
+        <v>3.245379309647568</v>
       </c>
       <c r="D4" t="n">
-        <v>20.39621054751223</v>
+        <v>3.314384213970737</v>
       </c>
       <c r="E4" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F4" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.14134375305981</v>
+        <v>3.92296835987222</v>
       </c>
       <c r="D5" t="n">
-        <v>10.16026395578123</v>
+        <v>1.651042892814451</v>
       </c>
       <c r="E5" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F5" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.93061458368832</v>
+        <v>4.701224869849353</v>
       </c>
       <c r="D6" t="n">
-        <v>23.36126838575107</v>
+        <v>3.796206112684549</v>
       </c>
       <c r="E6" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F6" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.37633754567615</v>
+        <v>2.173654851172375</v>
       </c>
       <c r="D7" t="n">
-        <v>13.25565084625359</v>
+        <v>2.154043262516208</v>
       </c>
       <c r="E7" t="n">
-        <v>5.631706419663304</v>
+        <v>0.9151522931952871</v>
       </c>
       <c r="F7" t="n">
-        <v>6.034474776068165</v>
+        <v>0.9806021511110766</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
